--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B7" t="n">
-        <v>103937</v>
+        <v>103947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R7" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119439</v>
+        <v>122119438</v>
       </c>
       <c r="B8" t="n">
-        <v>103937</v>
+        <v>103947</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,14 +1448,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626441</v>
+        <v>626435</v>
       </c>
       <c r="R8" t="n">
-        <v>6925461</v>
+        <v>6925367</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0445</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
+          <t>sandig, hästbetad gräsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122119439</v>
+        <v>122119438</v>
       </c>
       <c r="B7" t="n">
-        <v>103947</v>
+        <v>103960</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626441</v>
+        <v>626435</v>
       </c>
       <c r="R7" t="n">
-        <v>6925461</v>
+        <v>6925367</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0445</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
+          <t>sandig, hästbetad gräsmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B8" t="n">
-        <v>103947</v>
+        <v>103960</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,14 +1448,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R8" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B7" t="n">
-        <v>103960</v>
+        <v>103965</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,14 +1327,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R7" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119439</v>
+        <v>122119438</v>
       </c>
       <c r="B8" t="n">
-        <v>103960</v>
+        <v>103965</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,14 +1448,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626441</v>
+        <v>626435</v>
       </c>
       <c r="R8" t="n">
-        <v>6925461</v>
+        <v>6925367</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0445</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
+          <t>sandig, hästbetad gräsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122119439</v>
       </c>
       <c r="B7" t="n">
-        <v>103965</v>
+        <v>103974</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,11 +1304,6 @@
       </c>
       <c r="E7" t="n">
         <v>563</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Sanddraba</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1411,7 +1406,7 @@
         <v>122119438</v>
       </c>
       <c r="B8" t="n">
-        <v>103965</v>
+        <v>103974</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,11 +1420,6 @@
       </c>
       <c r="E8" t="n">
         <v>563</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sanddraba</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1287,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122119439</v>
+        <v>122119438</v>
       </c>
       <c r="B7" t="n">
-        <v>103974</v>
+        <v>103987</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,6 +1304,11 @@
       </c>
       <c r="E7" t="n">
         <v>563</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sanddraba</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1322,14 +1327,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626441</v>
+        <v>626435</v>
       </c>
       <c r="R7" t="n">
-        <v>6925461</v>
+        <v>6925367</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1356,7 +1361,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0445</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1381,7 +1386,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
+          <t>sandig, hästbetad gräsmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1403,10 +1408,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B8" t="n">
-        <v>103974</v>
+        <v>103987</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,6 +1425,11 @@
       </c>
       <c r="E8" t="n">
         <v>563</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sanddraba</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1438,14 +1448,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R8" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1472,7 +1482,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1507,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>122119438</v>
       </c>
       <c r="B7" t="n">
-        <v>103987</v>
+        <v>104000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>122119439</v>
       </c>
       <c r="B8" t="n">
-        <v>103987</v>
+        <v>104000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1287,7 +1287,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B7" t="n">
         <v>104000</v>
@@ -1327,14 +1327,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R7" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1408,7 +1408,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119439</v>
+        <v>122119438</v>
       </c>
       <c r="B8" t="n">
         <v>104000</v>
@@ -1448,14 +1448,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626441</v>
+        <v>626435</v>
       </c>
       <c r="R8" t="n">
-        <v>6925461</v>
+        <v>6925367</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0445</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
+          <t>sandig, hästbetad gräsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,69 +1159,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114378067</v>
+        <v>97313696</v>
       </c>
       <c r="B6" t="n">
-        <v>57206</v>
+        <v>98865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102622</v>
+        <v>222295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Släda, Mpd</t>
+          <t>Stömsta 1, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626684</v>
+        <v>626435</v>
       </c>
       <c r="R6" t="n">
-        <v>6925371</v>
+        <v>6925367</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,22 +1233,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>05:05</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:05</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,75 +1247,92 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Granfeldt</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Granfeldt</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Hans Rydberg, Stefan Grundström, Håkan Sundin, Jan-Olof Tedebrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122119439</v>
+        <v>114378067</v>
       </c>
       <c r="B7" t="n">
-        <v>104000</v>
+        <v>57206</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>563</v>
+        <v>102622</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sanddraba</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Draba nemorosa</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Släda, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626441</v>
+        <v>626684</v>
       </c>
       <c r="R7" t="n">
-        <v>6925461</v>
+        <v>6925371</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,19 +1354,24 @@
           <t>Alnö</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Y-Sun-0444</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,38 +1380,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>ängsbacke</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Granfeldt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B8" t="n">
-        <v>104000</v>
+        <v>104003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1448,14 +1438,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R8" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,7 +1472,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1507,7 +1497,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1522,6 +1512,127 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122119438</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104003</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>563</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sanddraba</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Draba nemorosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stömstad, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626435</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6925367</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Y-Sun-0445</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>sandig, hästbetad gräsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1398,7 +1398,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122119439</v>
+        <v>122119438</v>
       </c>
       <c r="B8" t="n">
         <v>104003</v>
@@ -1438,14 +1438,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626441</v>
+        <v>626435</v>
       </c>
       <c r="R8" t="n">
-        <v>6925461</v>
+        <v>6925367</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0445</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
+          <t>sandig, hästbetad gräsmark</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122119438</v>
+        <v>122119439</v>
       </c>
       <c r="B9" t="n">
         <v>104003</v>
@@ -1559,14 +1559,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626435</v>
+        <v>626441</v>
       </c>
       <c r="R9" t="n">
-        <v>6925367</v>
+        <v>6925461</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0444</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>ängsbacke</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>97313696</v>
       </c>
       <c r="B6" t="n">
-        <v>98865</v>
+        <v>98866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>122119438</v>
       </c>
       <c r="B8" t="n">
-        <v>104003</v>
+        <v>104004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>122119439</v>
       </c>
       <c r="B9" t="n">
-        <v>104003</v>
+        <v>104004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>97313696</v>
       </c>
       <c r="B6" t="n">
-        <v>98866</v>
+        <v>98869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>122119438</v>
       </c>
       <c r="B8" t="n">
-        <v>104004</v>
+        <v>104007</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Y-Sun-0445</t>
+          <t>Y-Sun-0273</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1522,7 +1522,7 @@
         <v>122119439</v>
       </c>
       <c r="B9" t="n">
-        <v>104004</v>
+        <v>104007</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Y-Sun-0444</t>
+          <t>Y-Sun-0272</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>97313696</v>
       </c>
       <c r="B6" t="n">
-        <v>98972</v>
+        <v>98980</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>97313696</v>
       </c>
       <c r="B6" t="n">
-        <v>98980</v>
+        <v>98982</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1162,7 +1162,7 @@
         <v>97313696</v>
       </c>
       <c r="B6" t="n">
-        <v>98982</v>
+        <v>98990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1159,57 +1159,69 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97313696</v>
+        <v>114378067</v>
       </c>
       <c r="B6" t="n">
-        <v>98990</v>
+        <v>57206</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222295</v>
+        <v>102622</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Latourr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stömsta 1, Mpd</t>
+          <t>Släda, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626435</v>
+        <v>626684</v>
       </c>
       <c r="R6" t="n">
-        <v>6925367</v>
+        <v>6925371</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,12 +1245,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,396 +1269,21 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Thomas Granfeldt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Stefan Grundström, Håkan Sundin, Jan-Olof Tedebrand</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>114378067</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57206</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>102622</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Pärluggla</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Aegolius funereus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Släda, Mpd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>626684</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6925371</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Alnö</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-01-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>05:05</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-01-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>05:05</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
           <t>Thomas Granfeldt</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Thomas Granfeldt</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>122119438</v>
-      </c>
-      <c r="B8" t="n">
-        <v>104007</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>563</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Sanddraba</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Draba nemorosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Stömstad, Mpd</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>626435</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6925367</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Alnö</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Y-Sun-0273</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>sandig, hästbetad gräsmark</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>122119439</v>
-      </c>
-      <c r="B9" t="n">
-        <v>104007</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>563</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Sanddraba</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Draba nemorosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Släda, 600 m S om, Mpd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>626441</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6925461</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Alnö</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Y-Sun-0272</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>ängsbacke</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,6 +1284,130 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125058287</v>
+      </c>
+      <c r="B7" t="n">
+        <v>105365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>981</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vit sminkrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buglossoides arvensis var. arvensis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stömsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626565</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6925569</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>58 plantor varav 22 blommande. Växer längs på stigen, i backen bakom bostadshuset.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas, Kerstin Stickler</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>125058287</v>
       </c>
       <c r="B7" t="n">
-        <v>105365</v>
+        <v>105541</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -1290,12 +1290,7 @@
         <v>125058287</v>
       </c>
       <c r="B7" t="n">
-        <v>105541</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105574</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94055437</v>
+        <v>102343</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Rödprick</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Arthonia helvola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Släda, 600 m S om, Mpd</t>
+          <t>Slädabäcken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626441.2940687061</v>
+        <v>626615</v>
       </c>
       <c r="R2" t="n">
-        <v>6925461.250314044</v>
+        <v>6925321</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>på bark vid basen av levande gråal, i gråalsumpskog av högörttyp med strutbräken längs med bäck, skuggigt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,37 +764,37 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ängsbacke</t>
-        </is>
-      </c>
+          <t>gråalsumpskog</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gråal</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering av sandmaskros Y-län</t>
-        </is>
-      </c>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94055143</v>
+        <v>102354</v>
       </c>
       <c r="B3" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222295</v>
+        <v>96</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Rödprick</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Arthonia helvola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>(Nyl.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Slädabäcken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626434.6428970041</v>
+        <v>626632</v>
       </c>
       <c r="R3" t="n">
-        <v>6925367.372217922</v>
+        <v>6925328</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på bark vid basen av levande hägg angripen av häggspinnmal, i närheten finns flera grova rönnar med Pachyphiale fagicola, måbär växer också i närheten, i gråalsumpskog av högörttyp med strutbräken längs med bäck, skuggigt, på litet krön mellan bäckarna</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,72 +880,72 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
-        </is>
-      </c>
+          <t>gråalsumpskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # hägg</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Håkan Sundin, Jan-Olof Tedebrand, Stefan Grundström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering av sandmaskros Y-län</t>
-        </is>
-      </c>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94055280</v>
+        <v>102356</v>
       </c>
       <c r="B4" t="n">
-        <v>101928</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>563</v>
+        <v>96</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sanddraba</t>
+          <t>Rödprick</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Draba nemorosa</t>
+          <t>Arthonia helvola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stömstad, Mpd</t>
+          <t>Slädabäcken, Alnön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626434.6428970041</v>
+        <v>626635</v>
       </c>
       <c r="R4" t="n">
-        <v>6925367.372217922</v>
+        <v>6925322</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,22 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-09-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>på bark vid basen av dubbelstammig rönn (25 + 20 cm dbh, ca 80 år gammal), skuggigt mellan rönnarna, i gråalsumpskog av högörttyp med strutbräken längs med bäck, skuggigt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +996,46 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>sandig, hästbetad gräsmark</t>
+          <t>gråalsumpskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rönn</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>2685</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Håkan Sundin, Jan-Olof Tedebrand, Stefan Grundström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventering av sandmaskros Y-län</t>
-        </is>
-      </c>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94055279</v>
+        <v>94055278</v>
       </c>
       <c r="B5" t="n">
-        <v>101928</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626441.2940687061</v>
+        <v>626514</v>
       </c>
       <c r="R5" t="n">
-        <v>6925461.250314044</v>
+        <v>6925559</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,19 +1100,9 @@
           <t>2021-06-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-06-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1127,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Rydberg, Håkan Sundin, Jan-Olof Tedebrand, Stefan Grundström</t>
+          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1159,69 +1138,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114378067</v>
+        <v>94055279</v>
       </c>
       <c r="B6" t="n">
-        <v>57454</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102622</v>
+        <v>563</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Draba nemorosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Släda, Mpd</t>
+          <t>Släda, 600 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626684</v>
+        <v>626441</v>
       </c>
       <c r="R6" t="n">
-        <v>6925371</v>
+        <v>6925461</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,99 +1203,86 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>05:05</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>05:05</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>ängsbacke</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Granfeldt</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Thomas Granfeldt</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av sandmaskros Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125058287</v>
+        <v>94055280</v>
       </c>
       <c r="B7" t="n">
-        <v>105574</v>
+        <v>104880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>981</v>
+        <v>563</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vit sminkrot</t>
+          <t>Sanddraba</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buglossoides arvensis var. arvensis</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Draba nemorosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stömsta, Mpd</t>
+          <t>Stömstad, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626565</v>
+        <v>626435</v>
       </c>
       <c r="R7" t="n">
-        <v>6925569</v>
+        <v>6925367</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1364,17 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>58 plantor varav 22 blommande. Växer längs på stigen, i backen bakom bostadshuset.</t>
+          <t>2021-06-03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1383,24 +1323,748 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sandig, hästbetad gräsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Grundström, Jan-Olof Tedebrand, Håkan Sundin, Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av sandmaskros Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125058287</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106499</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>981</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vit sminkrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Buglossoides arvensis var. arvensis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stömsta, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626565</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6925569</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Y-Sun-0367</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>58 plantor varav 22 blommande. Växer längs på stigen, i backen bakom bostadshuset.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Agneta Toomingas, Kerstin Stickler</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114378067</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57785</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Släda, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626684</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6925371</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-01-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>05:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Granfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Thomas Granfeldt</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>81021430</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Släda 200 (5), Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626926</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6925612</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Sun-0166</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-07-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Plantor räknats på ömse sidor om Vikmansvägen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Mager glesbeväxt öppen mark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Grafström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Grafström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94055437</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Släda, 600 m S om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626441</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6925461</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>ängsbacke</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Inventering av sandmaskros Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94055143</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stömstad, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626435</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6925367</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-06-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>sandig, hästbetad gräsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Hans Rydberg, Håkan Sundin, Jan-Olof Tedebrand, Stefan Grundström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Inventering av sandmaskros Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>89411880</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101794</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222929</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Backruta</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thalictrum simplex</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>bladfällning, vissnar</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Släda 200 (2), Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626909</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6925634</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alnö</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Arkiv-Y-Sun-0172</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tre delokaler 47+2+9 på tomten o angränsande mark</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Eva Grafström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Eva Grafström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 55854-2022 artfynd.xlsx
+++ b/artfynd/A 55854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102343</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102354</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102356</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
           <t>Inventering av sandmaskros Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94055278</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
           <t>Inventering av sandmaskros Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94055279</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Inventering av sandmaskros Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94055280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125058287</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114378067</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1727,6 +1772,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81021430</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1833,6 +1883,11 @@
           <t>Inventering av sandmaskros Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94055437</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1939,6 +1994,11 @@
           <t>Inventering av sandmaskros Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94055143</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2067,8 +2127,27 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89411880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>